--- a/june 2026/LMT_JUNE_26/SD/Sohail Traders SD.xlsx
+++ b/june 2026/LMT_JUNE_26/SD/Sohail Traders SD.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D15648-B8FC-4A31-82D9-1C699A3DB140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E14B73F-EF4D-4A2B-8776-1DA52350D680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3428,7 +3428,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -3456,7 +3456,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -4673,7 +4673,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -4701,7 +4701,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -5918,7 +5918,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -5946,7 +5946,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -7163,7 +7163,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -7191,7 +7191,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -8408,7 +8408,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -8436,7 +8436,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -9653,7 +9653,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -9681,7 +9681,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -10898,7 +10898,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -10926,7 +10926,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -12143,7 +12143,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -12171,7 +12171,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -13388,7 +13388,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -13416,7 +13416,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -14633,7 +14633,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -14661,7 +14661,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -18628,7 +18628,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -18656,7 +18656,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -19870,7 +19870,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -19898,7 +19898,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -21111,7 +21111,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -21139,7 +21139,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -22352,7 +22352,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -22380,7 +22380,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23598,7 +23598,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -23626,7 +23626,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23837,7 +23837,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>248050.38069600001</v>
+        <v>494173.47691200004</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -24141,11 +24141,11 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>0</v>
+        <v>520</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>37772.800000000003</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -24157,23 +24157,23 @@
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>6043.6480000000001</v>
+        <v>12087.296</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>-6043.6480000000001</v>
+        <v>25685.504000000001</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>7395.9142400000001</v>
+        <v>14376.32768</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>195.62533120000001</v>
+        <v>389.17315840000003</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>1547.8915711999998</v>
+        <v>40451.004838400004</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24211,11 +24211,11 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20</f>
-        <v>0</v>
+        <v>920</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>66828.800000000003</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
@@ -24227,23 +24227,23 @@
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>10692.608</v>
+        <v>21385.216</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>-10692.608</v>
+        <v>45443.584000000003</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>13085.079040000001</v>
+        <v>25435.041280000001</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>346.10635520000005</v>
+        <v>688.53712640000003</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>2738.5773952000004</v>
+        <v>71567.162406400006</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24281,11 +24281,11 @@
       <c r="G21" s="113"/>
       <c r="H21" s="171">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21</f>
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>69734.399999999994</v>
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
@@ -24297,23 +24297,23 @@
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>11157.503999999999</v>
+        <v>22315.007999999998</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>-11157.503999999999</v>
+        <v>47419.391999999993</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>13653.995519999999</v>
+        <v>26540.912639999995</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>361.15445759999994</v>
+        <v>718.47352319999993</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>2857.6459775999997</v>
+        <v>74678.778163199982</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24351,11 +24351,11 @@
       <c r="G22" s="113"/>
       <c r="H22" s="171">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22+'17'!H22+'18'!H22</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>62768.000000000007</v>
       </c>
       <c r="J22" s="171">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -24363,27 +24363,27 @@
       </c>
       <c r="K22" s="171">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>2196.8800000000006</v>
+        <v>4393.7600000000011</v>
       </c>
       <c r="L22" s="174">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>6276.8000000000011</v>
+        <v>12553.600000000002</v>
       </c>
       <c r="M22" s="117">
         <f t="shared" si="2"/>
-        <v>-8473.6800000000021</v>
+        <v>45820.639999999999</v>
       </c>
       <c r="N22" s="100">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>11944.750400000001</v>
+        <v>23889.500800000002</v>
       </c>
       <c r="O22" s="100">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>331.19535200000007</v>
+        <v>662.39070400000014</v>
       </c>
       <c r="P22" s="119">
         <f t="shared" si="0"/>
-        <v>3802.2657519999989</v>
+        <v>70372.531503999999</v>
       </c>
       <c r="T22" s="162" t="str">
         <f>+'9'!A5</f>
@@ -24541,7 +24541,7 @@
       <c r="B25" s="227"/>
       <c r="C25" s="228">
         <f>H25/40</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25" s="222"/>
       <c r="E25" s="222"/>
@@ -24552,11 +24552,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>237104</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24564,27 +24564,27 @@
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
-        <v>2196.8800000000006</v>
+        <v>4393.7600000000011</v>
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>34170.560000000005</v>
+        <v>68341.12000000001</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>-36367.440000000002</v>
+        <v>164369.12</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>46079.739199999996</v>
+        <v>90241.782399999996</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>1234.0814960000002</v>
+        <v>2458.5745120000001</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>10946.380695999998</v>
+        <v>257069.47691199998</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>248050.38069600001</v>
+        <v>494173.47691200004</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24825,7 +24825,7 @@
       <c r="O35" s="239"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>0</v>
+        <v>237104</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24846,7 +24846,7 @@
       <c r="O36" s="241"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>34170.560000000005</v>
+        <v>68341.12000000001</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24867,7 +24867,7 @@
       <c r="O37" s="241"/>
       <c r="P37" s="153">
         <f>K25</f>
-        <v>2196.8800000000006</v>
+        <v>4393.7600000000011</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24889,7 +24889,7 @@
       <c r="O38" s="241"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>-36367.440000000002</v>
+        <v>164369.12</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>46079.739199999996</v>
+        <v>90241.782399999996</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24936,7 +24936,7 @@
       <c r="O40" s="243"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>9712.299199999994</v>
+        <v>254610.90239999999</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24961,7 +24961,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>242.80747999999986</v>
+        <v>6365.2725600000003</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24971,7 +24971,7 @@
       <c r="O42" s="221"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>9955.1066799999935</v>
+        <v>260976.17496</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25143,7 +25143,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -25171,7 +25171,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -25641,10 +25641,13 @@
       <c r="G19" s="113">
         <v>13</v>
       </c>
-      <c r="H19" s="114"/>
+      <c r="H19" s="114">
+        <f>G19*40</f>
+        <v>520</v>
+      </c>
       <c r="I19" s="115">
         <f t="shared" si="3"/>
-        <v>37772.800000000003</v>
+        <v>75545.600000000006</v>
       </c>
       <c r="J19" s="102">
         <f>G19*2</f>
@@ -25656,23 +25659,23 @@
       </c>
       <c r="L19" s="104">
         <f t="shared" si="5"/>
-        <v>6043.6480000000001</v>
+        <v>12087.296</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="6"/>
-        <v>31729.152000000002</v>
+        <v>63458.304000000004</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>7395.9142400000001</v>
+        <v>14376.32768</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="1"/>
-        <v>195.62533120000001</v>
+        <v>389.17315840000003</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="2"/>
-        <v>39320.691571199997</v>
+        <v>78223.804838399999</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25702,13 +25705,16 @@
       <c r="G20" s="113">
         <v>23</v>
       </c>
-      <c r="H20" s="114"/>
+      <c r="H20" s="114">
+        <f t="shared" ref="H20:H22" si="7">G20*40</f>
+        <v>920</v>
+      </c>
       <c r="I20" s="115">
         <f t="shared" si="3"/>
-        <v>66828.800000000003</v>
+        <v>133657.60000000001</v>
       </c>
       <c r="J20" s="102">
-        <f t="shared" ref="J20:J21" si="7">G20*2</f>
+        <f t="shared" ref="J20:J21" si="8">G20*2</f>
         <v>46</v>
       </c>
       <c r="K20" s="1">
@@ -25717,23 +25723,23 @@
       </c>
       <c r="L20" s="104">
         <f t="shared" si="5"/>
-        <v>10692.608</v>
+        <v>21385.216</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="6"/>
-        <v>56136.192000000003</v>
+        <v>112272.38400000001</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>13085.079040000001</v>
+        <v>25435.041280000001</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>346.10635520000005</v>
+        <v>688.53712640000003</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>69567.377395200005</v>
+        <v>138395.96240640001</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25763,13 +25769,16 @@
       <c r="G21" s="113">
         <v>24</v>
       </c>
-      <c r="H21" s="114"/>
+      <c r="H21" s="114">
+        <f t="shared" si="7"/>
+        <v>960</v>
+      </c>
       <c r="I21" s="115">
         <f t="shared" si="3"/>
-        <v>69734.399999999994</v>
+        <v>139468.79999999999</v>
       </c>
       <c r="J21" s="102">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>48</v>
       </c>
       <c r="K21" s="1">
@@ -25778,23 +25787,23 @@
       </c>
       <c r="L21" s="104">
         <f t="shared" si="5"/>
-        <v>11157.503999999999</v>
+        <v>22315.007999999998</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="6"/>
-        <v>58576.895999999993</v>
+        <v>117153.79199999999</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>13653.995519999999</v>
+        <v>26540.912639999995</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="1"/>
-        <v>361.15445759999994</v>
+        <v>718.47352319999993</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="2"/>
-        <v>72592.045977599992</v>
+        <v>144413.17816319998</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25824,35 +25833,38 @@
       <c r="G22" s="113">
         <v>40</v>
       </c>
-      <c r="H22" s="114"/>
+      <c r="H22" s="114">
+        <f t="shared" si="7"/>
+        <v>1600</v>
+      </c>
       <c r="I22" s="115">
         <f t="shared" si="3"/>
-        <v>62768.000000000007</v>
+        <v>125536.00000000001</v>
       </c>
       <c r="J22" s="102"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>2196.8800000000006</v>
+        <v>4393.7600000000011</v>
       </c>
       <c r="L22" s="119">
         <f>I22*10%</f>
-        <v>6276.8000000000011</v>
+        <v>12553.600000000002</v>
       </c>
       <c r="M22" s="117">
         <f t="shared" si="6"/>
-        <v>54294.320000000007</v>
+        <v>108588.64000000001</v>
       </c>
       <c r="N22" s="117">
         <f t="shared" si="0"/>
-        <v>11944.750400000001</v>
+        <v>23889.500800000002</v>
       </c>
       <c r="O22" s="118">
         <f t="shared" si="1"/>
-        <v>331.19535200000007</v>
+        <v>662.39070400000014</v>
       </c>
       <c r="P22" s="119">
         <f t="shared" si="2"/>
-        <v>66570.265752000007</v>
+        <v>133140.53150400001</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25887,11 +25899,11 @@
       </c>
       <c r="J23" s="116"/>
       <c r="K23" s="1">
-        <f t="shared" ref="K23:K24" si="8">I23*3.5%</f>
+        <f t="shared" ref="K23:K24" si="9">I23*3.5%</f>
         <v>0</v>
       </c>
       <c r="L23" s="119">
-        <f t="shared" ref="L23:L24" si="9">I23*$L$13</f>
+        <f t="shared" ref="L23:L24" si="10">I23*$L$13</f>
         <v>0</v>
       </c>
       <c r="M23" s="117">
@@ -25943,11 +25955,11 @@
       </c>
       <c r="J24" s="129"/>
       <c r="K24" s="130">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="L24" s="131">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="M24" s="132">
@@ -25977,44 +25989,44 @@
       <c r="E25" s="222"/>
       <c r="F25" s="253"/>
       <c r="G25" s="134">
-        <f t="shared" ref="G25:M25" si="10">SUM(G16:G24)</f>
+        <f t="shared" ref="G25:M25" si="11">SUM(G16:G24)</f>
         <v>100</v>
       </c>
       <c r="H25" s="135">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>4000</v>
       </c>
       <c r="I25" s="136">
-        <f t="shared" si="10"/>
-        <v>237104</v>
+        <f t="shared" si="11"/>
+        <v>474208</v>
       </c>
       <c r="J25" s="182">
         <f>SUM(J16:J21)</f>
         <v>120</v>
       </c>
       <c r="K25" s="138">
-        <f t="shared" si="10"/>
-        <v>2196.8800000000006</v>
+        <f t="shared" si="11"/>
+        <v>4393.7600000000011</v>
       </c>
       <c r="L25" s="139">
-        <f t="shared" si="10"/>
-        <v>34170.560000000005</v>
+        <f t="shared" si="11"/>
+        <v>68341.12000000001</v>
       </c>
       <c r="M25" s="140">
-        <f t="shared" si="10"/>
-        <v>200736.56</v>
+        <f t="shared" si="11"/>
+        <v>401473.12</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>46079.739199999996</v>
+        <v>90241.782399999996</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>1234.0814960000002</v>
+        <v>2458.5745120000001</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>248050.38069599998</v>
+        <v>494173.47691199998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26064,7 +26076,7 @@
       <c r="O28" s="239"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>237104</v>
+        <v>474208</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26085,7 +26097,7 @@
       <c r="O29" s="241"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>34170.560000000005</v>
+        <v>68341.12000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26106,7 +26118,7 @@
       <c r="O30" s="241"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>2196.8800000000006</v>
+        <v>4393.7600000000011</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26128,7 +26140,7 @@
       <c r="O31" s="241"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>200736.56</v>
+        <v>401473.12</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26153,7 +26165,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>46079.739199999996</v>
+        <v>90241.782399999996</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26175,7 +26187,7 @@
       <c r="O33" s="243"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>246816.29920000001</v>
+        <v>491714.90240000002</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26200,7 +26212,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>1234.081496</v>
+        <v>2458.5745120000001</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26210,7 +26222,7 @@
       <c r="O35" s="221"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>248050.38069600001</v>
+        <v>494173.47691200004</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26278,7 +26290,7 @@
     <mergeCell ref="K4:M4"/>
     <mergeCell ref="N4:P4"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>$XFC$3:$XFC$4</formula1>
     </dataValidation>
@@ -26293,7 +26305,7 @@
   <pageSetup scale="83" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0300-000003000000}">
           <x14:formula1>
             <xm:f>Sheet2!$B$6:$B$14</xm:f>
@@ -26382,7 +26394,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -26410,7 +26422,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -27627,7 +27639,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -27655,7 +27667,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -28871,7 +28883,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -28899,7 +28911,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -30116,7 +30128,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -30144,7 +30156,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -31362,7 +31374,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46195</v>
+        <v>46234</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -31390,7 +31402,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46194</v>
+        <v>46233</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
